--- a/data/merged/2026-09-09/MERGED_DE_Mite-Vacuum_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_DE_Mite-Vacuum_2026-09-09.xlsx
@@ -7084,50 +7084,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7453,7 +7409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18590,7 +18546,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -18603,23 +18559,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Filter-Set für VCH 4 UVClean Matratzenreiniger, Ersatzfilter aus Motorschutzfilter und Schaumfilter für hygienische R</t>
+          <t>Beghdhu Milbensauger für matratzen mit UV-Lichts20Kpa Matratzenreiniger Bettstaubsauger, Mini Handstaubsauger für Matratzen</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0GH912PFJ?psc=1</t>
+          <t>https://www.amazon.de/dp/B0HG11J16S?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81CSvqgRiOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="M50" s="14"/>
@@ -18640,7 +18596,7 @@
       <c r="AB50"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE50" s="15"/>
       <c r="AF50" s="21">
@@ -18688,112 +18644,6 @@
       <c r="BP50" s="23"/>
       <c r="BQ50" s="23"/>
       <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.deundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Beghdhu Milbensauger für matratzen mit UV-Lichts20Kpa Matratzenreiniger Bettstaubsauger, Mini Handstaubsauger für Matratzen</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/dp/B0HG11J16S?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19173,18 +19023,13 @@
     <hyperlink ref="M49" r:id="rId372" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N49" r:id="rId373"/>
     <hyperlink ref="AW49" r:id="rId374" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3N5OUC8NSOQ84"/>
-    <hyperlink ref="C50" r:id="rId375" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
+    <hyperlink ref="C50" r:id="rId375" tooltip="https://www.amazon.de/dp/B0HG11J16S"/>
     <hyperlink ref="G50" r:id="rId376" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J50" r:id="rId377" tooltip="https://www.amazon.de/dp/B0GH912PFJ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId378" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81CSvqgRiOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId379" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
-    <hyperlink ref="C51" r:id="rId380" tooltip="https://www.amazon.de/dp/B0HG11J16S"/>
-    <hyperlink ref="G51" r:id="rId381" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J51" r:id="rId382" tooltip="https://www.amazon.de/dp/B0HG11J16S?psc=1"/>
-    <hyperlink ref="K51" r:id="rId383" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId384" tooltip="https://www.amazon.de/dp/B0HG11J16S"/>
+    <hyperlink ref="J50" r:id="rId377" tooltip="https://www.amazon.de/dp/B0HG11J16S?psc=1"/>
+    <hyperlink ref="K50" r:id="rId378" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId379" tooltip="https://www.amazon.de/dp/B0HG11J16S"/>
   </hyperlinks>
-  <drawing r:id="rId385"/>
+  <drawing r:id="rId380"/>
 </worksheet>
 </file>
 
